--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 10/02. Trả bảo hành/TBH_GPSGlobal_201026.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 10/02. Trả bảo hành/TBH_GPSGlobal_201026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 10\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C64058-C734-4DB9-9022-9110A05F94D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFCD30A-CE74-477F-8026-1636EF80B556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -510,6 +510,45 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -528,47 +567,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1066,69 +1066,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46"/>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="47" t="s">
+      <c r="A1" s="42"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="48" t="s">
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="50"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="51" t="s">
+      <c r="A3" s="42"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="53"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="49"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="54" t="s">
+      <c r="A4" s="42"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="56"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="52"/>
     </row>
     <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
@@ -1221,7 +1221,7 @@
       <c r="B11" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="40" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="21" t="s">
@@ -1247,7 +1247,7 @@
       <c r="B12" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="40" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="21"/>
@@ -1271,7 +1271,7 @@
       <c r="B13" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="40" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="21"/>
@@ -1295,7 +1295,7 @@
       <c r="B14" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="41" t="s">
         <v>27</v>
       </c>
       <c r="D14" s="21" t="s">
@@ -1326,34 +1326,34 @@
       <c r="I15" s="9"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
       <c r="F16" s="26"/>
-      <c r="G16" s="45" t="s">
+      <c r="G16" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
       <c r="F17" s="39"/>
-      <c r="G17" s="44" t="s">
+      <c r="G17" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="27"/>
@@ -1400,19 +1400,19 @@
       <c r="I21" s="16"/>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
       <c r="F22" s="14"/>
-      <c r="G22" s="43" t="s">
+      <c r="G22" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
@@ -1426,17 +1426,12 @@
       <c r="I23" s="7"/>
     </row>
     <row r="25" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="55"/>
     </row>
     <row r="64" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="A16:E16"/>
@@ -1445,6 +1440,11 @@
     <mergeCell ref="G16:I16"/>
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="G22:I22"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="97" orientation="landscape" r:id="rId1"/>
@@ -1461,33 +1461,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="45" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
       <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57" t="s">
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
       <c r="I2" s="15"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1535,18 +1535,18 @@
       <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43" t="s">
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
       <c r="I7" s="14"/>
     </row>
   </sheetData>
